--- a/samples/Ridgeline Facades Pty Ltd (ACN 444 555 666) - Harrow Street - Commercial Summary Schedule.xlsx
+++ b/samples/Ridgeline Facades Pty Ltd (ACN 444 555 666) - Harrow Street - Commercial Summary Schedule.xlsx
@@ -296,46 +296,46 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF404040"/>
+      <color rgb="FF1F5FC4"/>
       <sz val="18"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF5A5A5A"/>
+      <color rgb="FF555E6D"/>
       <sz val="11.5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF5A5A5A"/>
+      <color rgb="FF555E6D"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF5A5A5A"/>
+      <color rgb="FF555E6D"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF2E2E2E"/>
+      <color rgb="FF24282E"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF2E2E2E"/>
+      <color rgb="FF24282E"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF404040"/>
+      <color rgb="FF1F5FC4"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF8A5A2B"/>
+      <color rgb="FF3C4149"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
@@ -347,52 +347,52 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF404040"/>
+      <color rgb="FF1F5FC4"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF5A5A5A"/>
+      <color rgb="FF555E6D"/>
       <sz val="9.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF2E2E2E"/>
+      <color rgb="FF24282E"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF2E2E2E"/>
+      <color rgb="FF24282E"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A5A5A"/>
+      <color rgb="FF555E6D"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF2E2E2E"/>
+      <color rgb="FF24282E"/>
       <sz val="9.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF2E2E2E"/>
+      <color rgb="FF24282E"/>
       <sz val="9.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A5A5A"/>
+      <color rgb="FF555E6D"/>
       <sz val="8.5"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF404040"/>
+      <color rgb="FF1F5FC4"/>
       <sz val="12"/>
       <name val="Calibri"/>
     </font>
@@ -430,27 +430,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF404040"/>
+        <fgColor rgb="FF1F5FC4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6F6F6"/>
+        <fgColor rgb="FFF5F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDEDED"/>
+        <fgColor rgb="FFE6E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4EDE4"/>
+        <fgColor rgb="FFECECED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8A5A2B"/>
+        <fgColor rgb="FF3C4149"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +472,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,52 +481,52 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color rgb="FF2B2B2B"/>
+        <color rgb="FF184A99"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </left>
       <right style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </right>
       <top style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC8C8C8"/>
+        <color rgb="FFC6CBD2"/>
       </left>
       <right style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </right>
       <top style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF8A5A2B"/>
+        <color rgb="FF3C4149"/>
       </left>
       <right style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </right>
       <top style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -535,7 +535,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFC8C8C8"/>
+        <color rgb="FFC6CBD2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -543,7 +543,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFE2E2E2"/>
+        <color rgb="FFE0E2E6"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1151,7 +1151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF404040"/>
+    <tabColor rgb="FF1F5FC4"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
@@ -1589,7 +1589,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFC8C8C8"/>
+    <tabColor rgb="FFC6CBD2"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:C24"/>

--- a/samples/Ridgeline Facades Pty Ltd (ACN 444 555 666) - Harrow Street - Commercial Summary Schedule.xlsx
+++ b/samples/Ridgeline Facades Pty Ltd (ACN 444 555 666) - Harrow Street - Commercial Summary Schedule.xlsx
@@ -286,7 +286,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00&quot; excluding GST&quot;"/>
     <numFmt numFmtId="165" formatCode="d mmmm yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -301,29 +301,29 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF555E6D"/>
+      <color rgb="FF525252"/>
       <sz val="11.5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF555E6D"/>
+      <color rgb="FF525252"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF555E6D"/>
+      <color rgb="FF525252"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF24282E"/>
+      <color rgb="FF1A1A1A"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF24282E"/>
+      <color rgb="FF1A1A1A"/>
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
@@ -335,8 +335,14 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF3C4149"/>
+      <color rgb="FF40464F"/>
       <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -346,47 +352,35 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF525252"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1A1A1A"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF525252"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1A1A1A"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
-      <color rgb="FF1F5FC4"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF555E6D"/>
+      <color rgb="FF1A1A1A"/>
       <sz val="9.5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF24282E"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF24282E"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <i/>
-      <color rgb="FF555E6D"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF24282E"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF24282E"/>
-      <sz val="9.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF555E6D"/>
+      <color rgb="FF525252"/>
       <sz val="8.5"/>
       <name val="Calibri"/>
     </font>
@@ -421,7 +415,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -435,7 +429,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
+        <fgColor rgb="FFFAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -445,12 +449,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFECECED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3C4149"/>
+        <fgColor rgb="FF40464F"/>
       </patternFill>
     </fill>
     <fill>
@@ -459,7 +458,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -472,7 +471,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,52 +480,61 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color rgb="FF184A99"/>
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF40464F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </left>
       <right style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </right>
       <top style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC6CBD2"/>
+        <color rgb="FFCFCFCF"/>
       </left>
       <right style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </right>
       <top style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF3C4149"/>
+        <color rgb="FF40464F"/>
       </left>
       <right style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </right>
       <top style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -535,7 +543,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFC6CBD2"/>
+        <color rgb="FFCFCFCF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -543,7 +551,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFE0E2E6"/>
+        <color rgb="FFE3E3E3"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -588,73 +596,73 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1589,7 +1597,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFC6CBD2"/>
+    <tabColor rgb="FFCFCFCF"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:C24"/>
